--- a/artfynd/A 33104-2024 artfynd.xlsx
+++ b/artfynd/A 33104-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>120005959</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33104-2024 artfynd.xlsx
+++ b/artfynd/A 33104-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>106858297</v>
       </c>
       <c r="B2" t="n">
-        <v>85156</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,7 +695,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius caesiostramineus s. lat.</t>
+          <t>Cortinarius caesiostramineus s.lat.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490824.2169483112</v>
+        <v>490824</v>
       </c>
       <c r="R2" t="n">
-        <v>6566282.26917197</v>
+        <v>6566282</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,19 +750,9 @@
           <t>2017-09-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,16 +783,11 @@
         <v>120005959</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -904,6 +884,206 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>54631429</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korset, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>490732</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6566353</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kärr, vid dike</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>54631432</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Korset, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>490732</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6566353</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kärr, vid dike</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
